--- a/LISTAS/mi/SOGA REVESTIDA.xlsx
+++ b/LISTAS/mi/SOGA REVESTIDA.xlsx
@@ -912,16 +912,12 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="36" t="n">
-        <v>45163.60918407294</v>
+        <v>45232</v>
       </c>
       <c r="E1" s="25" t="n"/>
       <c r="F1" s="25" t="n"/>
       <c r="G1" s="25" t="n"/>
     </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
     <row r="6">
       <c r="F6" s="29" t="n"/>
     </row>
@@ -935,7 +931,6 @@
     <row r="8" ht="22.5" customHeight="1" s="35">
       <c r="A8" s="1" t="n"/>
     </row>
-    <row r="9"/>
     <row r="10" ht="41.25" customHeight="1" s="35">
       <c r="A10" s="2" t="inlineStr">
         <is>
@@ -996,7 +991,7 @@
         </is>
       </c>
       <c r="D14" s="16" t="n">
-        <v>41.25</v>
+        <v>43.2</v>
       </c>
     </row>
     <row r="15" ht="22.5" customHeight="1" s="35">
@@ -1016,7 +1011,7 @@
         </is>
       </c>
       <c r="D15" s="17" t="n">
-        <v>58.875</v>
+        <v>61.8</v>
       </c>
     </row>
     <row r="16" ht="22.5" customHeight="1" s="35">
@@ -1036,7 +1031,7 @@
         </is>
       </c>
       <c r="D16" s="17" t="n">
-        <v>81.875</v>
+        <v>88.40000000000001</v>
       </c>
     </row>
     <row r="17" ht="23.25" customHeight="1" s="35" thickBot="1">
@@ -1056,7 +1051,7 @@
         </is>
       </c>
       <c r="D17" s="18" t="n">
-        <v>162.5</v>
+        <v>154</v>
       </c>
     </row>
     <row r="18" ht="20.25" customHeight="1" s="35">
@@ -1066,7 +1061,7 @@
     <row r="19" ht="54" customHeight="1" s="35">
       <c r="A19" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">
+          <t>
 </t>
         </is>
       </c>
@@ -1088,16 +1083,6 @@
       <c r="D22" s="9" t="n"/>
       <c r="F22" s="26" t="n"/>
     </row>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
-    <row r="31"/>
-    <row r="32"/>
     <row r="33" ht="33.75" customHeight="1" s="35">
       <c r="A33" s="34" t="inlineStr">
         <is>
@@ -1145,7 +1130,9 @@
         </is>
       </c>
       <c r="C36" s="32" t="n"/>
-      <c r="D36" s="27" t="n"/>
+      <c r="D36" s="27" t="n">
+        <v>31.973</v>
+      </c>
     </row>
     <row r="37" ht="39" customHeight="1" s="35">
       <c r="A37" s="12" t="inlineStr">
@@ -1163,10 +1150,10 @@
     </row>
   </sheetData>
   <mergeCells count="4">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B36:C36"/>
     <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B36:C36"/>
     <mergeCell ref="A33:D33"/>
-    <mergeCell ref="A1:D1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/mi/SOGA REVESTIDA.xlsx
+++ b/LISTAS/mi/SOGA REVESTIDA.xlsx
@@ -912,7 +912,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="36" t="n">
-        <v>45232</v>
+        <v>45237</v>
       </c>
       <c r="E1" s="25" t="n"/>
       <c r="F1" s="25" t="n"/>

--- a/LISTAS/mi/SOGA REVESTIDA.xlsx
+++ b/LISTAS/mi/SOGA REVESTIDA.xlsx
@@ -912,7 +912,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="36" t="n">
-        <v>45237</v>
+        <v>45238</v>
       </c>
       <c r="E1" s="25" t="n"/>
       <c r="F1" s="25" t="n"/>
@@ -1150,10 +1150,10 @@
     </row>
   </sheetData>
   <mergeCells count="4">
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="A33:D33"/>
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="A33:D33"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/mi/SOGA REVESTIDA.xlsx
+++ b/LISTAS/mi/SOGA REVESTIDA.xlsx
@@ -912,7 +912,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="36" t="n">
-        <v>45238</v>
+        <v>45244</v>
       </c>
       <c r="E1" s="25" t="n"/>
       <c r="F1" s="25" t="n"/>

--- a/LISTAS/mi/SOGA REVESTIDA.xlsx
+++ b/LISTAS/mi/SOGA REVESTIDA.xlsx
@@ -912,7 +912,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="36" t="n">
-        <v>45244</v>
+        <v>45253</v>
       </c>
       <c r="E1" s="25" t="n"/>
       <c r="F1" s="25" t="n"/>

--- a/LISTAS/mi/SOGA REVESTIDA.xlsx
+++ b/LISTAS/mi/SOGA REVESTIDA.xlsx
@@ -912,7 +912,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="36" t="n">
-        <v>45253</v>
+        <v>45256</v>
       </c>
       <c r="E1" s="25" t="n"/>
       <c r="F1" s="25" t="n"/>
@@ -1150,10 +1150,10 @@
     </row>
   </sheetData>
   <mergeCells count="4">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B36:C36"/>
     <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B36:C36"/>
     <mergeCell ref="A33:D33"/>
-    <mergeCell ref="A1:D1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/mi/SOGA REVESTIDA.xlsx
+++ b/LISTAS/mi/SOGA REVESTIDA.xlsx
@@ -912,7 +912,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="36" t="n">
-        <v>45256</v>
+        <v>45266</v>
       </c>
       <c r="E1" s="25" t="n"/>
       <c r="F1" s="25" t="n"/>

--- a/LISTAS/mi/SOGA REVESTIDA.xlsx
+++ b/LISTAS/mi/SOGA REVESTIDA.xlsx
@@ -912,12 +912,16 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="36" t="n">
-        <v>45266</v>
+        <v>45258.54560342059</v>
       </c>
       <c r="E1" s="25" t="n"/>
       <c r="F1" s="25" t="n"/>
       <c r="G1" s="25" t="n"/>
     </row>
+    <row r="2"/>
+    <row r="3"/>
+    <row r="4"/>
+    <row r="5"/>
     <row r="6">
       <c r="F6" s="29" t="n"/>
     </row>
@@ -931,6 +935,7 @@
     <row r="8" ht="22.5" customHeight="1" s="35">
       <c r="A8" s="1" t="n"/>
     </row>
+    <row r="9"/>
     <row r="10" ht="41.25" customHeight="1" s="35">
       <c r="A10" s="2" t="inlineStr">
         <is>
@@ -991,7 +996,7 @@
         </is>
       </c>
       <c r="D14" s="16" t="n">
-        <v>43.2</v>
+        <v>72.40000000000001</v>
       </c>
     </row>
     <row r="15" ht="22.5" customHeight="1" s="35">
@@ -1011,7 +1016,7 @@
         </is>
       </c>
       <c r="D15" s="17" t="n">
-        <v>61.8</v>
+        <v>103.5</v>
       </c>
     </row>
     <row r="16" ht="22.5" customHeight="1" s="35">
@@ -1031,7 +1036,7 @@
         </is>
       </c>
       <c r="D16" s="17" t="n">
-        <v>88.40000000000001</v>
+        <v>148</v>
       </c>
     </row>
     <row r="17" ht="23.25" customHeight="1" s="35" thickBot="1">
@@ -1051,7 +1056,7 @@
         </is>
       </c>
       <c r="D17" s="18" t="n">
-        <v>154</v>
+        <v>255</v>
       </c>
     </row>
     <row r="18" ht="20.25" customHeight="1" s="35">
@@ -1061,7 +1066,7 @@
     <row r="19" ht="54" customHeight="1" s="35">
       <c r="A19" s="19" t="inlineStr">
         <is>
-          <t>
+          <t xml:space="preserve">
 </t>
         </is>
       </c>
@@ -1083,6 +1088,16 @@
       <c r="D22" s="9" t="n"/>
       <c r="F22" s="26" t="n"/>
     </row>
+    <row r="23"/>
+    <row r="24"/>
+    <row r="25"/>
+    <row r="26"/>
+    <row r="27"/>
+    <row r="28"/>
+    <row r="29"/>
+    <row r="30"/>
+    <row r="31"/>
+    <row r="32"/>
     <row r="33" ht="33.75" customHeight="1" s="35">
       <c r="A33" s="34" t="inlineStr">
         <is>
@@ -1130,9 +1145,7 @@
         </is>
       </c>
       <c r="C36" s="32" t="n"/>
-      <c r="D36" s="27" t="n">
-        <v>31.973</v>
-      </c>
+      <c r="D36" s="27" t="n"/>
     </row>
     <row r="37" ht="39" customHeight="1" s="35">
       <c r="A37" s="12" t="inlineStr">
@@ -1150,10 +1163,10 @@
     </row>
   </sheetData>
   <mergeCells count="4">
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="A33:D33"/>
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="A33:D33"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="0" verticalDpi="0"/>

--- a/LISTAS/mi/SOGA REVESTIDA.xlsx
+++ b/LISTAS/mi/SOGA REVESTIDA.xlsx
@@ -912,16 +912,12 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="36" t="n">
-        <v>45258.54560342059</v>
+        <v>45286</v>
       </c>
       <c r="E1" s="25" t="n"/>
       <c r="F1" s="25" t="n"/>
       <c r="G1" s="25" t="n"/>
     </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
     <row r="6">
       <c r="F6" s="29" t="n"/>
     </row>
@@ -935,7 +931,6 @@
     <row r="8" ht="22.5" customHeight="1" s="35">
       <c r="A8" s="1" t="n"/>
     </row>
-    <row r="9"/>
     <row r="10" ht="41.25" customHeight="1" s="35">
       <c r="A10" s="2" t="inlineStr">
         <is>
@@ -996,7 +991,7 @@
         </is>
       </c>
       <c r="D14" s="16" t="n">
-        <v>72.40000000000001</v>
+        <v>43.2</v>
       </c>
     </row>
     <row r="15" ht="22.5" customHeight="1" s="35">
@@ -1016,7 +1011,7 @@
         </is>
       </c>
       <c r="D15" s="17" t="n">
-        <v>103.5</v>
+        <v>61.8</v>
       </c>
     </row>
     <row r="16" ht="22.5" customHeight="1" s="35">
@@ -1036,7 +1031,7 @@
         </is>
       </c>
       <c r="D16" s="17" t="n">
-        <v>148</v>
+        <v>88.40000000000001</v>
       </c>
     </row>
     <row r="17" ht="23.25" customHeight="1" s="35" thickBot="1">
@@ -1056,7 +1051,7 @@
         </is>
       </c>
       <c r="D17" s="18" t="n">
-        <v>255</v>
+        <v>154</v>
       </c>
     </row>
     <row r="18" ht="20.25" customHeight="1" s="35">
@@ -1066,7 +1061,7 @@
     <row r="19" ht="54" customHeight="1" s="35">
       <c r="A19" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">
+          <t>
 </t>
         </is>
       </c>
@@ -1088,16 +1083,6 @@
       <c r="D22" s="9" t="n"/>
       <c r="F22" s="26" t="n"/>
     </row>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
-    <row r="31"/>
-    <row r="32"/>
     <row r="33" ht="33.75" customHeight="1" s="35">
       <c r="A33" s="34" t="inlineStr">
         <is>
@@ -1145,7 +1130,11 @@
         </is>
       </c>
       <c r="C36" s="32" t="n"/>
-      <c r="D36" s="27" t="n"/>
+      <c r="D36" s="27" t="inlineStr">
+        <is>
+          <t>********</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="39" customHeight="1" s="35">
       <c r="A37" s="12" t="inlineStr">
